--- a/data/trans_orig/Q5406-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5406-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2007</t>
+          <t>Población según si es capaz de tomar medicación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,62 +881,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1895</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>8247</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1895</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6615</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53430</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82878</t>
+          <t>81246</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,62 +1224,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>8572</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1751</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>8807</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,62 +1337,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>3844</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>4265</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42002</t>
+          <t>41109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56672</t>
+          <t>56559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1762</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5993</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>24,69%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5596</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5663</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6371</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>11978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60336</t>
+          <t>60311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69190</t>
+          <t>69192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82106</t>
+          <t>81912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92541</t>
+          <t>92549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,62 +2136,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1824</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5716</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26268</t>
+          <t>26366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>233423</t>
+          <t>234496</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>249528</t>
+          <t>249723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79763</t>
+          <t>79245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>317864</t>
+          <t>317718</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334685</t>
+          <t>334040</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45161</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53770</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76881</t>
+          <t>77347</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91119</t>
+          <t>91022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128007</t>
+          <t>127435</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142900</t>
+          <t>143218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28666</t>
+          <t>28424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>27188</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>383725</t>
+          <t>384069</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>406186</t>
+          <t>405212</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>386691</t>
+          <t>387909</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>408981</t>
+          <t>410184</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39967</t>
+          <t>40173</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>42185</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71149</t>
+          <t>71563</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>457727</t>
+          <t>456880</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>478888</t>
+          <t>479271</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>618481</t>
+          <t>619463</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>645241</t>
+          <t>645182</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1084650</t>
+          <t>1083500</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1119944</t>
+          <t>1119277</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2012</t>
+          <t>Población según si es capaz de tomar medicación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,97 +4159,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2151</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39353</t>
+          <t>37575</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59515</t>
+          <t>59522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64696</t>
+          <t>64593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77277</t>
+          <t>77286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>17956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102097</t>
+          <t>100744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116317</t>
+          <t>115538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47015</t>
+          <t>47625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152814</t>
+          <t>152155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168909</t>
+          <t>169014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30551</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>34018</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191539</t>
+          <t>192084</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>213215</t>
+          <t>213002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50434</t>
+          <t>50346</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58999</t>
+          <t>59003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>246545</t>
+          <t>246163</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>269220</t>
+          <t>269329</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>20621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24569</t>
+          <t>24763</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31793</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>20321</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40226</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82737</t>
+          <t>81711</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96378</t>
+          <t>95557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143749</t>
+          <t>145034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165700</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>232530</t>
+          <t>232585</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>257634</t>
+          <t>257565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25846</t>
+          <t>26432</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26062</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16454</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36349</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>37329</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>340778</t>
+          <t>339428</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>364867</t>
+          <t>365056</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>341261</t>
+          <t>342527</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>367002</t>
+          <t>367752</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22566</t>
+          <t>22393</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47588</t>
+          <t>43613</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36368</t>
+          <t>36321</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67389</t>
+          <t>67409</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53498</t>
+          <t>51851</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>39623</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>68212</t>
+          <t>67601</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70717</t>
+          <t>69771</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>109623</t>
+          <t>107588</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>485441</t>
+          <t>488591</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>518208</t>
+          <t>520073</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>635661</t>
+          <t>638610</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>672757</t>
+          <t>674227</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1138083</t>
+          <t>1137152</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1185609</t>
+          <t>1186699</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2016</t>
+          <t>Población según si es capaz de tomar medicación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,97 +7585,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2085</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7698,97 +7698,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7430</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>20,14%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7079</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>19,19%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6426</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68647</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>99109</t>
+          <t>98647</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8041,97 +8041,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2217</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>48261</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61079</t>
+          <t>61333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69946</t>
+          <t>69934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,62 +8532,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>4034</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4087</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112962</t>
+          <t>112502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119487</t>
+          <t>119477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>41255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156605</t>
+          <t>156540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165302</t>
+          <t>165659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>14238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20993</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187977</t>
+          <t>187300</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>198926</t>
+          <t>198862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83358</t>
+          <t>82642</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96946</t>
+          <t>96937</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>275574</t>
+          <t>277723</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>293595</t>
+          <t>293917</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>28118</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126429</t>
+          <t>125842</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139143</t>
+          <t>139152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140292</t>
+          <t>139606</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154591</t>
+          <t>154535</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>273064</t>
+          <t>269714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291115</t>
+          <t>289412</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>33936</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>33936</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>366407</t>
+          <t>367271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>392292</t>
+          <t>393027</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>366407</t>
+          <t>367271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>392292</t>
+          <t>393027</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>24117</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>31809</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>27077</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27204</t>
+          <t>28786</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55846</t>
+          <t>57084</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45057</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>77488</t>
+          <t>78017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>556532</t>
+          <t>556935</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>574821</t>
+          <t>574788</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>698773</t>
+          <t>700233</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>732507</t>
+          <t>731971</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1263834</t>
+          <t>1264220</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1301112</t>
+          <t>1302965</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2023</t>
+          <t>Población según si es capaz de tomar medicación en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,62 +11046,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -11124,97 +11124,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>992</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3973</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>104379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61348</t>
+          <t>62009</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168099</t>
+          <t>167787</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172511</t>
+          <t>172508</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -11467,97 +11467,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>966</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2926</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>469</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91924</t>
+          <t>91430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41926</t>
+          <t>42117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46376</t>
+          <t>46353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135785</t>
+          <t>136362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140998</t>
+          <t>140977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,62 +11958,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95516</t>
+          <t>94697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101094</t>
+          <t>101095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46793</t>
+          <t>46670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51311</t>
+          <t>51340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144149</t>
+          <t>143159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151365</t>
+          <t>151303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>30653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>212295</t>
+          <t>212559</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225601</t>
+          <t>226218</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>309500</t>
+          <t>309224</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>325691</t>
+          <t>325753</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>524352</t>
+          <t>523486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>557471</t>
+          <t>556648</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14948</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>26602</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82443</t>
+          <t>81841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89288</t>
+          <t>89118</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>173310</t>
+          <t>172853</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186559</t>
+          <t>185785</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>258875</t>
+          <t>259281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>272773</t>
+          <t>273331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19228</t>
+          <t>18887</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36352</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>21050</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37526</t>
+          <t>36795</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>270911</t>
+          <t>269360</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>288003</t>
+          <t>287885</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>273150</t>
+          <t>273617</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>290634</t>
+          <t>291827</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40112</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>27233</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69081</t>
+          <t>70371</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50059</t>
+          <t>46882</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>91257</t>
+          <t>91591</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>599568</t>
+          <t>599963</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>616616</t>
+          <t>617156</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>915525</t>
+          <t>915429</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>972580</t>
+          <t>978203</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1528030</t>
+          <t>1526765</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1584658</t>
+          <t>1585993</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5406-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5406-Clase-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53642</t>
+          <t>53663</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81246</t>
+          <t>82861</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41109</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>57188</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60311</t>
+          <t>59981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69192</t>
+          <t>69138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81912</t>
+          <t>82046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92549</t>
+          <t>92650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23302</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26366</t>
+          <t>25300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>234496</t>
+          <t>234068</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>249723</t>
+          <t>249266</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79245</t>
+          <t>78970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>317718</t>
+          <t>318357</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334040</t>
+          <t>333828</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>44965</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53668</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77347</t>
+          <t>77707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91022</t>
+          <t>91244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127435</t>
+          <t>128191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143218</t>
+          <t>143062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>19523</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>28724</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27188</t>
+          <t>28765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>384069</t>
+          <t>383027</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>405212</t>
+          <t>405368</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>387909</t>
+          <t>386790</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>410184</t>
+          <t>408604</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30432</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40173</t>
+          <t>39750</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>39299</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42185</t>
+          <t>42509</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71563</t>
+          <t>70292</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>456880</t>
+          <t>458826</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>479271</t>
+          <t>479156</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>619463</t>
+          <t>617242</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>645182</t>
+          <t>645162</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1083500</t>
+          <t>1085740</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1119277</t>
+          <t>1118771</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37575</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62143</t>
+          <t>61713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59522</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64593</t>
+          <t>64651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77286</t>
+          <t>77298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100744</t>
+          <t>99780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115538</t>
+          <t>116287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47625</t>
+          <t>47843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152155</t>
+          <t>153755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169014</t>
+          <t>169929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15703</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13463</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>35044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>192084</t>
+          <t>191752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>213002</t>
+          <t>212989</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50346</t>
+          <t>50485</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59003</t>
+          <t>59009</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>246163</t>
+          <t>245594</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>269329</t>
+          <t>269890</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24763</t>
+          <t>24736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29491</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20321</t>
+          <t>19772</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41717</t>
+          <t>41483</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81711</t>
+          <t>82454</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95557</t>
+          <t>95699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145034</t>
+          <t>143710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164769</t>
+          <t>164385</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>232585</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>257565</t>
+          <t>257887</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26432</t>
+          <t>25457</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25938</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36929</t>
+          <t>37398</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37329</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>339428</t>
+          <t>339945</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>365056</t>
+          <t>364703</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>342527</t>
+          <t>342695</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>367752</t>
+          <t>367414</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22393</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43613</t>
+          <t>47341</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36321</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67409</t>
+          <t>64944</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>36800</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>67601</t>
+          <t>66386</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>69771</t>
+          <t>70199</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>107588</t>
+          <t>109065</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>488591</t>
+          <t>487365</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>520073</t>
+          <t>519776</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>638610</t>
+          <t>640095</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>674227</t>
+          <t>675945</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1137152</t>
+          <t>1139776</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1186699</t>
+          <t>1185861</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98647</t>
+          <t>98489</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>987</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48261</t>
+          <t>48652</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61333</t>
+          <t>61719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69934</t>
+          <t>69945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112502</t>
+          <t>112488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119477</t>
+          <t>119479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>40650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156540</t>
+          <t>157346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165659</t>
+          <t>165260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19696</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187300</t>
+          <t>187536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>198862</t>
+          <t>198837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82642</t>
+          <t>82582</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96937</t>
+          <t>96892</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>277723</t>
+          <t>276999</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>293917</t>
+          <t>294116</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>27476</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125842</t>
+          <t>125967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139152</t>
+          <t>138842</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139606</t>
+          <t>140260</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154535</t>
+          <t>154659</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269714</t>
+          <t>272405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289412</t>
+          <t>291057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>18340</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>18340</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33936</t>
+          <t>33695</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33936</t>
+          <t>33695</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>367271</t>
+          <t>366129</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>393027</t>
+          <t>391645</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>367271</t>
+          <t>366129</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>393027</t>
+          <t>391645</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24117</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28786</t>
+          <t>27935</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>57084</t>
+          <t>56554</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44241</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>78017</t>
+          <t>76564</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>556935</t>
+          <t>555653</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>574788</t>
+          <t>574168</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>700233</t>
+          <t>697663</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>731971</t>
+          <t>732468</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1264220</t>
+          <t>1264079</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1302965</t>
+          <t>1300625</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>612</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>612</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -11086,12 +11086,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -11232,27 +11232,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106952</t>
+          <t>119789</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104379</t>
+          <t>117208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11267,27 +11267,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64329</t>
+          <t>73498</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62009</t>
+          <t>70710</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>171281</t>
+          <t>193287</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>167787</t>
+          <t>190268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172508</t>
+          <t>194555</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -11542,12 +11542,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>488</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -11688,27 +11688,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94381</t>
+          <t>104114</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91430</t>
+          <t>100629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44923</t>
+          <t>53247</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42117</t>
+          <t>50349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46353</t>
+          <t>54820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>139304</t>
+          <t>157361</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136362</t>
+          <t>153901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140977</t>
+          <t>159143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>501</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>99094</t>
+          <t>109511</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94697</t>
+          <t>105822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101095</t>
+          <t>111496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49619</t>
+          <t>54394</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46670</t>
+          <t>50443</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>56222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>148712</t>
+          <t>163905</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143159</t>
+          <t>158836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151303</t>
+          <t>166762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52336</t>
+          <t>57502</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52336</t>
+          <t>57502</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52336</t>
+          <t>57502</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154404</t>
+          <t>169973</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154404</t>
+          <t>169973</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154404</t>
+          <t>169973</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>219909</t>
+          <t>240742</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>212559</t>
+          <t>232858</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>226218</t>
+          <t>246404</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>320989</t>
+          <t>124435</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>309224</t>
+          <t>120351</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>325753</t>
+          <t>127351</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>540898</t>
+          <t>365176</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>523486</t>
+          <t>356672</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>556648</t>
+          <t>372527</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>237577</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>237577</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237577</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564270</t>
+          <t>390218</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564270</t>
+          <t>390218</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564270</t>
+          <t>390218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>337</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>14711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>10414</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14719</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16355</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26602</t>
+          <t>28270</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>86499</t>
+          <t>95195</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81841</t>
+          <t>91333</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89118</t>
+          <t>98014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>180143</t>
+          <t>193726</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172853</t>
+          <t>186181</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>185785</t>
+          <t>200055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>266642</t>
+          <t>288922</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259281</t>
+          <t>280430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>273331</t>
+          <t>296329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>219866</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>219866</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>219866</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13321,17 +13321,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18887</t>
+          <t>20394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>518</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28457</t>
+          <t>29552</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>37376</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36795</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -13512,27 +13512,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>280148</t>
+          <t>302147</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>269360</t>
+          <t>292403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>287885</t>
+          <t>310891</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>282862</t>
+          <t>304905</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>273617</t>
+          <t>294940</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>291827</t>
+          <t>313307</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>345137</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>345137</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>345137</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324284</t>
+          <t>348413</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324284</t>
+          <t>348413</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324284</t>
+          <t>348413</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35383</t>
+          <t>35011</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>30519</t>
+          <t>32317</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>24323</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>22086</t>
+          <t>23046</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>45180</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70371</t>
+          <t>65565</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>74358</t>
+          <t>78452</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46882</t>
+          <t>66340</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>91591</t>
+          <t>91577</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>609547</t>
+          <t>672109</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>599963</t>
+          <t>662036</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>617156</t>
+          <t>679779</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>940150</t>
+          <t>801448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>915429</t>
+          <t>788335</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>978203</t>
+          <t>813684</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1549698</t>
+          <t>1473556</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1526765</t>
+          <t>1457224</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1585993</t>
+          <t>1488127</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>637432</t>
+          <t>700995</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>637432</t>
+          <t>700995</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>637432</t>
+          <t>700995</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1017143</t>
+          <t>883330</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1017143</t>
+          <t>883330</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1017143</t>
+          <t>883330</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1654575</t>
+          <t>1584325</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1654575</t>
+          <t>1584325</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1654575</t>
+          <t>1584325</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
